--- a/artfynd/A 3671-2026 artfynd.xlsx
+++ b/artfynd/A 3671-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122824921</v>
+        <v>122824934</v>
       </c>
       <c r="B2" t="n">
-        <v>97333</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -719,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>612568</v>
+        <v>612571</v>
       </c>
       <c r="R2" t="n">
-        <v>6510272</v>
+        <v>6510274</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,43 +777,37 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122824934</v>
+        <v>122824769</v>
       </c>
       <c r="B3" t="n">
-        <v>95925</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92567</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>53</v>
+        <v>6031</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -826,10 +815,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>612571</v>
+        <v>612626</v>
       </c>
       <c r="R3" t="n">
-        <v>6510274</v>
+        <v>6510239</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -856,12 +845,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-10-30</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-10-30</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,12 +881,7 @@
         <v>122824819</v>
       </c>
       <c r="B4" t="n">
-        <v>91589</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92567</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -993,6 +977,312 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>122824731</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57899</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100067</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Havsörn</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Haliaeetus albicilla</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Projektarbete kryptogamer, Srm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>612656</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6510184</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Nyköping</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Nyköping</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-10-29</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-10-29</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Sofia Fast</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Sofia Fast</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>122825104</v>
+      </c>
+      <c r="B6" t="n">
+        <v>4781</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>102306</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Granbarkgnagare</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Microbregma emarginatum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Projektarbete kryptogamer, Srm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>612581</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6510397</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Nyköping</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Nyköping</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-10-30</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-10-30</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Sofia Fast</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Sofia Fast</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>122824921</v>
+      </c>
+      <c r="B7" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Projektarbete kryptogamer, Srm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>612568</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6510272</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Nyköping</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Nyköping</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-10-30</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-10-30</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Sofia Fast</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Sofia Fast</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 3671-2026 artfynd.xlsx
+++ b/artfynd/A 3671-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122824934</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -875,6 +885,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122824769</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -976,6 +991,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122824819</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1077,6 +1097,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122824731</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1180,6 +1205,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122825104</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1282,8 +1312,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122824921</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>